--- a/Excel/家具房间表.xlsx
+++ b/Excel/家具房间表.xlsx
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -37,8 +37,12 @@
       <color rgb="00888888"/>
       <sz val="9"/>
     </font>
+    <font>
+      <i val="1"/>
+      <color rgb="00666666"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -48,6 +52,16 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="006E243E"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="004F81BD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DCE6F1"/>
       </patternFill>
     </fill>
   </fills>
@@ -63,10 +77,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -432,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:P6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -486,6 +506,46 @@
           <t>初始货币</t>
         </is>
       </c>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>访客区左</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="inlineStr">
+        <is>
+          <t>访客区下</t>
+        </is>
+      </c>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>访客区右</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="inlineStr">
+        <is>
+          <t>访客区上</t>
+        </is>
+      </c>
+      <c r="M1" s="3" t="inlineStr">
+        <is>
+          <t>入口区左</t>
+        </is>
+      </c>
+      <c r="N1" s="3" t="inlineStr">
+        <is>
+          <t>入口区下</t>
+        </is>
+      </c>
+      <c r="O1" s="3" t="inlineStr">
+        <is>
+          <t>入口区右</t>
+        </is>
+      </c>
+      <c r="P1" s="3" t="inlineStr">
+        <is>
+          <t>入口区上</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -528,6 +588,46 @@
           <t>startCredit</t>
         </is>
       </c>
+      <c r="I2" s="4" t="inlineStr">
+        <is>
+          <t>visitorWalkArea.xMin</t>
+        </is>
+      </c>
+      <c r="J2" s="4" t="inlineStr">
+        <is>
+          <t>visitorWalkArea.yMin</t>
+        </is>
+      </c>
+      <c r="K2" s="4" t="inlineStr">
+        <is>
+          <t>visitorWalkArea.xMax</t>
+        </is>
+      </c>
+      <c r="L2" s="4" t="inlineStr">
+        <is>
+          <t>visitorWalkArea.yMax</t>
+        </is>
+      </c>
+      <c r="M2" s="4" t="inlineStr">
+        <is>
+          <t>visitorEntryArea.xMin</t>
+        </is>
+      </c>
+      <c r="N2" s="4" t="inlineStr">
+        <is>
+          <t>visitorEntryArea.yMin</t>
+        </is>
+      </c>
+      <c r="O2" s="4" t="inlineStr">
+        <is>
+          <t>visitorEntryArea.xMax</t>
+        </is>
+      </c>
+      <c r="P2" s="4" t="inlineStr">
+        <is>
+          <t>visitorEntryArea.yMax</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -551,11 +651,33 @@
           <t>Assets/PC ui/Scene/房间.png</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
         <v>2480</v>
       </c>
+      <c r="I3" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.233</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.233</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0.41</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -579,11 +701,33 @@
           <t>Assets/PC ui/Scene/房间-1.png</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
         <v>2480</v>
       </c>
+      <c r="I4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.234</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.365</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.234</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0.4</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -607,11 +751,33 @@
           <t>Assets/PC ui/Scene/房间-2.png</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
         <v>2480</v>
       </c>
+      <c r="I5" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.231</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.231</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0.36</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -635,10 +801,32 @@
           <t>Assets/PC ui/Scene/房间-3.png</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
         <v>2480</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.231</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.231</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0.36</v>
       </c>
     </row>
   </sheetData>
@@ -1217,7 +1405,6 @@
           <t>wall</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
       <c r="E3" t="n">
         <v>9</v>
       </c>
@@ -1246,7 +1433,6 @@
           <t>wall</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
       <c r="E4" t="n">
         <v>16</v>
       </c>
@@ -1275,7 +1461,6 @@
           <t>floor</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
       <c r="E5" t="n">
         <v>9</v>
       </c>
@@ -1304,7 +1489,6 @@
           <t>floor</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
       <c r="E6" t="n">
         <v>13</v>
       </c>
@@ -1333,7 +1517,6 @@
           <t>wall</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
       <c r="E7" t="n">
         <v>5</v>
       </c>
@@ -1362,7 +1545,6 @@
           <t>floor</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
       <c r="E8" t="n">
         <v>5</v>
       </c>
@@ -1391,7 +1573,6 @@
           <t>floor</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
       <c r="E9" t="n">
         <v>15</v>
       </c>
@@ -1420,7 +1601,6 @@
           <t>floor</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
       <c r="E10" t="n">
         <v>23</v>
       </c>
@@ -1449,7 +1629,6 @@
           <t>wall</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
       <c r="E11" t="n">
         <v>10</v>
       </c>
@@ -1478,7 +1657,6 @@
           <t>floor</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
       <c r="E12" t="n">
         <v>9</v>
       </c>
@@ -1507,7 +1685,6 @@
           <t>floor</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
       <c r="E13" t="n">
         <v>21</v>
       </c>
@@ -1536,7 +1713,6 @@
           <t>floor</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
       <c r="E14" t="n">
         <v>0</v>
       </c>
@@ -1565,7 +1741,6 @@
           <t>floor</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
       <c r="E15" t="n">
         <v>5</v>
       </c>
@@ -1594,7 +1769,6 @@
           <t>wall</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
       <c r="E16" t="n">
         <v>15</v>
       </c>
@@ -1623,7 +1797,6 @@
           <t>floor</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
       <c r="E17" t="n">
         <v>18</v>
       </c>

--- a/Excel/家具房间表.xlsx
+++ b/Excel/家具房间表.xlsx
@@ -1003,7 +1003,7 @@
         <v>27</v>
       </c>
       <c r="E4" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F4" t="n">
         <v>60</v>
@@ -1073,7 +1073,7 @@
         <v>27</v>
       </c>
       <c r="E6" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F6" t="n">
         <v>60</v>
@@ -1143,7 +1143,7 @@
         <v>27</v>
       </c>
       <c r="E8" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F8" t="n">
         <v>60</v>
@@ -1213,7 +1213,7 @@
         <v>27</v>
       </c>
       <c r="E10" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F10" t="n">
         <v>60</v>
@@ -1397,7 +1397,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>016</t>
+          <t>landscape_poster_02</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1425,7 +1425,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>007</t>
+          <t>hanging_plant_01</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1453,7 +1453,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>002</t>
+          <t>armchair_01</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1465,7 +1465,7 @@
         <v>9</v>
       </c>
       <c r="F5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1481,7 +1481,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>005</t>
+          <t>round_table_01</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1493,7 +1493,7 @@
         <v>13</v>
       </c>
       <c r="F6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>018</t>
+          <t>landscape_poster_03</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1537,7 +1537,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>024</t>
+          <t>single_sofa_02</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1549,7 +1549,7 @@
         <v>5</v>
       </c>
       <c r="F8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -1565,7 +1565,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>036</t>
+          <t>cat_sofa_01</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1593,7 +1593,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>013</t>
+          <t>monstera_01</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>017</t>
+          <t>vintage_square_clock_02</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1649,7 +1649,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>043</t>
+          <t>round_table_02</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1661,7 +1661,7 @@
         <v>9</v>
       </c>
       <c r="F12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -1677,7 +1677,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>012</t>
+          <t>potted_plant_01</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1705,7 +1705,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>057</t>
+          <t>round_table_03</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1717,7 +1717,7 @@
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1733,7 +1733,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>053</t>
+          <t>potted_plant_02</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1761,7 +1761,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>037</t>
+          <t>vintage_square_clock_03</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>004</t>
+          <t>single_sofa_04</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">

--- a/Excel/家具房间表.xlsx
+++ b/Excel/家具房间表.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="40695" yWindow="2295" windowWidth="32805" windowHeight="18330" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="40695" yWindow="2295" windowWidth="32805" windowHeight="18330" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="房间" sheetId="1" state="visible" r:id="rId1"/>
@@ -654,11 +654,11 @@
         <v>1672</v>
       </c>
       <c r="D3" t="n">
-        <v>941</v>
+        <v>630</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Assets/PC ui/Scene/房间.png</t>
+          <t>Assets/PC ui/Scene/房间1.png</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -704,11 +704,11 @@
         <v>1672</v>
       </c>
       <c r="D4" t="n">
-        <v>941</v>
+        <v>635</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Assets/PC ui/Scene/房间-1.png</t>
+          <t>Assets/PC ui/Scene/房间2.png</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -754,11 +754,11 @@
         <v>1672</v>
       </c>
       <c r="D5" t="n">
-        <v>941</v>
+        <v>627</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Assets/PC ui/Scene/房间-2.png</t>
+          <t>Assets/PC ui/Scene/房间3.png</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -804,11 +804,11 @@
         <v>1672</v>
       </c>
       <c r="D6" t="n">
-        <v>941</v>
+        <v>623</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Assets/PC ui/Scene/房间-3.png</t>
+          <t>Assets/PC ui/Scene/房间4.png</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -841,6 +841,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
@@ -979,10 +980,10 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>51</v>
+        <v>34</v>
       </c>
       <c r="E3" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F3" t="n">
         <v>30</v>
@@ -991,10 +992,10 @@
         <v>30</v>
       </c>
       <c r="H3" t="n">
-        <v>56</v>
+        <v>316</v>
       </c>
       <c r="I3" t="n">
-        <v>110</v>
+        <v>75</v>
       </c>
       <c r="J3" t="n">
         <v>1</v>
@@ -1017,7 +1018,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E4" t="n">
         <v>6</v>
@@ -1026,16 +1027,16 @@
         <v>30</v>
       </c>
       <c r="G4" t="n">
-        <v>22.5</v>
+        <v>21.6</v>
       </c>
       <c r="H4" t="n">
-        <v>56</v>
+        <v>40</v>
       </c>
       <c r="I4" t="n">
-        <v>581</v>
+        <v>500</v>
       </c>
       <c r="J4" t="n">
-        <v>0.6</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="5">
@@ -1055,10 +1056,10 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>52</v>
+        <v>28</v>
       </c>
       <c r="E5" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F5" t="n">
         <v>30</v>
@@ -1067,10 +1068,10 @@
         <v>30</v>
       </c>
       <c r="H5" t="n">
-        <v>56</v>
+        <v>242</v>
       </c>
       <c r="I5" t="n">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="J5" t="n">
         <v>1</v>
@@ -1093,25 +1094,25 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F6" t="n">
         <v>30</v>
       </c>
       <c r="G6" t="n">
-        <v>22.5</v>
+        <v>21</v>
       </c>
       <c r="H6" t="n">
-        <v>56</v>
+        <v>40</v>
       </c>
       <c r="I6" t="n">
-        <v>581</v>
+        <v>530</v>
       </c>
       <c r="J6" t="n">
-        <v>0.45</v>
+        <v>0.74</v>
       </c>
     </row>
     <row r="7">
@@ -1131,10 +1132,10 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>52</v>
+        <v>24</v>
       </c>
       <c r="E7" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F7" t="n">
         <v>30</v>
@@ -1143,10 +1144,10 @@
         <v>30</v>
       </c>
       <c r="H7" t="n">
-        <v>56</v>
+        <v>562</v>
       </c>
       <c r="I7" t="n">
-        <v>110</v>
+        <v>75</v>
       </c>
       <c r="J7" t="n">
         <v>1</v>
@@ -1169,7 +1170,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E8" t="n">
         <v>6</v>
@@ -1178,16 +1179,16 @@
         <v>30</v>
       </c>
       <c r="G8" t="n">
-        <v>22.5</v>
+        <v>20.8</v>
       </c>
       <c r="H8" t="n">
-        <v>56</v>
+        <v>40</v>
       </c>
       <c r="I8" t="n">
-        <v>581</v>
+        <v>502</v>
       </c>
       <c r="J8" t="n">
-        <v>0.6</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="9">
@@ -1207,10 +1208,10 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="E9" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F9" t="n">
         <v>30</v>
@@ -1219,10 +1220,10 @@
         <v>30</v>
       </c>
       <c r="H9" t="n">
-        <v>56</v>
+        <v>130</v>
       </c>
       <c r="I9" t="n">
-        <v>110</v>
+        <v>59</v>
       </c>
       <c r="J9" t="n">
         <v>1</v>
@@ -1245,7 +1246,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E10" t="n">
         <v>6</v>
@@ -1254,13 +1255,13 @@
         <v>30</v>
       </c>
       <c r="G10" t="n">
-        <v>22.5</v>
+        <v>20.1</v>
       </c>
       <c r="H10" t="n">
-        <v>56</v>
+        <v>40</v>
       </c>
       <c r="I10" t="n">
-        <v>581</v>
+        <v>502</v>
       </c>
       <c r="J10" t="n">
         <v>0.88</v>

--- a/Excel/家具房间表.xlsx
+++ b/Excel/家具房间表.xlsx
@@ -665,28 +665,28 @@
         <v>2480</v>
       </c>
       <c r="I3" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="N3" t="n">
         <v>0.03</v>
       </c>
-      <c r="J3" t="n">
-        <v>0.233</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0.96</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0.233</v>
-      </c>
       <c r="O3" t="n">
-        <v>0.84</v>
+        <v>0.93</v>
       </c>
       <c r="P3" t="n">
-        <v>0.41</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="4">
@@ -715,28 +715,28 @@
         <v>2480</v>
       </c>
       <c r="I4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="N4" t="n">
         <v>0.03</v>
       </c>
-      <c r="J4" t="n">
-        <v>0.234</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0.97</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0.365</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0.234</v>
-      </c>
       <c r="O4" t="n">
-        <v>0.1</v>
+        <v>0.79</v>
       </c>
       <c r="P4" t="n">
-        <v>0.4</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="5">
@@ -765,28 +765,28 @@
         <v>2480</v>
       </c>
       <c r="I5" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="J5" t="n">
-        <v>0.231</v>
+        <v>0.02</v>
       </c>
       <c r="K5" t="n">
-        <v>0.97</v>
+        <v>0.95</v>
       </c>
       <c r="L5" t="n">
-        <v>0.36</v>
+        <v>0.13</v>
       </c>
       <c r="M5" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="P5" t="n">
         <v>0.12</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0.231</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0.36</v>
       </c>
     </row>
     <row r="6">
@@ -815,28 +815,28 @@
         <v>2480</v>
       </c>
       <c r="I6" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="N6" t="n">
         <v>0.03</v>
       </c>
-      <c r="J6" t="n">
-        <v>0.231</v>
-      </c>
-      <c r="K6" t="n">
+      <c r="O6" t="n">
         <v>0.97</v>
       </c>
-      <c r="L6" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0.231</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0.5</v>
-      </c>
       <c r="P6" t="n">
-        <v>0.36</v>
+        <v>0.12</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/家具房间表.xlsx
+++ b/Excel/家具房间表.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="40695" yWindow="2295" windowWidth="32805" windowHeight="18330" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="房间" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="网格" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="占用格" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="初始摆放" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="房间" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="网格" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="占用格" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="初始摆放" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -1021,7 +1021,7 @@
         <v>53</v>
       </c>
       <c r="E4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F4" t="n">
         <v>30</v>
@@ -1097,7 +1097,7 @@
         <v>53</v>
       </c>
       <c r="E6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F6" t="n">
         <v>30</v>
@@ -1173,7 +1173,7 @@
         <v>53</v>
       </c>
       <c r="E8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F8" t="n">
         <v>30</v>
@@ -1249,7 +1249,7 @@
         <v>53</v>
       </c>
       <c r="E10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F10" t="n">
         <v>30</v>
@@ -1499,7 +1499,7 @@
         <v>17</v>
       </c>
       <c r="F5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1527,7 +1527,7 @@
         <v>25</v>
       </c>
       <c r="F6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
         <v>9</v>
       </c>
       <c r="F8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
         <v>29</v>
       </c>
       <c r="F9" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -1639,7 +1639,7 @@
         <v>45</v>
       </c>
       <c r="F10" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -1695,7 +1695,7 @@
         <v>17</v>
       </c>
       <c r="F12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -1723,7 +1723,7 @@
         <v>41</v>
       </c>
       <c r="F13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -1751,7 +1751,7 @@
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1835,7 +1835,7 @@
         <v>35</v>
       </c>
       <c r="F17" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>

--- a/Excel/家具房间表.xlsx
+++ b/Excel/家具房间表.xlsx
@@ -645,10 +645,10 @@
         <v>0.8015</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>0.99</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>13.2</v>
       </c>
     </row>
     <row r="4">
@@ -707,10 +707,10 @@
         <v>0.8931</v>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>1.062</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>47.9</v>
       </c>
     </row>
     <row r="5">
@@ -769,10 +769,10 @@
         <v>0.7825</v>
       </c>
       <c r="S5" t="n">
-        <v>1</v>
+        <v>1.066</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>171.1</v>
       </c>
     </row>
     <row r="6">
@@ -831,10 +831,10 @@
         <v>0.8753</v>
       </c>
       <c r="S6" t="n">
-        <v>1</v>
+        <v>1.096</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>-117.3</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/家具房间表.xlsx
+++ b/Excel/家具房间表.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="房间" sheetId="1" r:id="Rbdd714245fb44674"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="网格" sheetId="2" r:id="Rec60b807645a4e58"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="占用格" sheetId="3" r:id="R25e5b29dac714813"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="初始摆放" sheetId="4" r:id="R6b9718284f244760"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="房间" sheetId="1" r:id="R189b7194a6704bed"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="网格" sheetId="2" r:id="R78b438265b7448e3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="占用格" sheetId="3" r:id="R859aedb57e0d4072"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="初始摆放" sheetId="4" r:id="R8884564ef8e2478e"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -968,16 +968,16 @@
         </x:is>
       </x:c>
       <x:c r="D3" t="n">
-        <x:v>34</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="E3" t="n">
-        <x:v>14</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="F3" t="n">
-        <x:v>30</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G3" t="n">
-        <x:v>30</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H3" t="n">
         <x:v>316</x:v>
@@ -1006,19 +1006,19 @@
         </x:is>
       </x:c>
       <x:c r="D4" t="n">
-        <x:v>53</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="E4" t="n">
-        <x:v>5</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="F4" t="n">
-        <x:v>30</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G4" t="n">
-        <x:v>21.6</x:v>
+        <x:v>10.8</x:v>
       </x:c>
       <x:c r="H4" t="n">
-        <x:v>40</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="I4" t="n">
         <x:v>500</x:v>
@@ -1044,16 +1044,16 @@
         </x:is>
       </x:c>
       <x:c r="D5" t="n">
-        <x:v>28</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="E5" t="n">
-        <x:v>13</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="F5" t="n">
-        <x:v>30</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G5" t="n">
-        <x:v>30</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H5" t="n">
         <x:v>242</x:v>
@@ -1082,19 +1082,19 @@
         </x:is>
       </x:c>
       <x:c r="D6" t="n">
-        <x:v>53</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="E6" t="n">
-        <x:v>4</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F6" t="n">
-        <x:v>30</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G6" t="n">
-        <x:v>21</x:v>
+        <x:v>10.5</x:v>
       </x:c>
       <x:c r="H6" t="n">
-        <x:v>40</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="I6" t="n">
         <x:v>530</x:v>
@@ -1120,16 +1120,16 @@
         </x:is>
       </x:c>
       <x:c r="D7" t="n">
-        <x:v>24</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="E7" t="n">
-        <x:v>14</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="F7" t="n">
-        <x:v>30</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G7" t="n">
-        <x:v>30</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H7" t="n">
         <x:v>562</x:v>
@@ -1158,19 +1158,19 @@
         </x:is>
       </x:c>
       <x:c r="D8" t="n">
-        <x:v>53</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="E8" t="n">
-        <x:v>5</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="F8" t="n">
-        <x:v>30</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G8" t="n">
-        <x:v>20.8</x:v>
+        <x:v>10.4</x:v>
       </x:c>
       <x:c r="H8" t="n">
-        <x:v>40</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="I8" t="n">
         <x:v>502</x:v>
@@ -1196,16 +1196,16 @@
         </x:is>
       </x:c>
       <x:c r="D9" t="n">
-        <x:v>46</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="E9" t="n">
-        <x:v>14</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="F9" t="n">
-        <x:v>30</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G9" t="n">
-        <x:v>30</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H9" t="n">
         <x:v>130</x:v>
@@ -1234,19 +1234,19 @@
         </x:is>
       </x:c>
       <x:c r="D10" t="n">
-        <x:v>53</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="E10" t="n">
-        <x:v>5</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="F10" t="n">
-        <x:v>30</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G10" t="n">
-        <x:v>20.1</x:v>
+        <x:v>10.05</x:v>
       </x:c>
       <x:c r="H10" t="n">
-        <x:v>40</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="I10" t="n">
         <x:v>502</x:v>
@@ -1417,10 +1417,10 @@
         </x:is>
       </x:c>
       <x:c r="E3" t="n">
-        <x:v>8</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F3" t="n">
-        <x:v>3</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="G3" t="inlineStr">
         <x:is>
@@ -1445,10 +1445,10 @@
         </x:is>
       </x:c>
       <x:c r="E4" t="n">
-        <x:v>25</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="F4" t="n">
-        <x:v>3</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="G4" t="inlineStr">
         <x:is>
@@ -1473,10 +1473,10 @@
         </x:is>
       </x:c>
       <x:c r="E5" t="n">
-        <x:v>17</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="F5" t="n">
-        <x:v>3</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="G5" t="inlineStr">
         <x:is>
@@ -1501,10 +1501,10 @@
         </x:is>
       </x:c>
       <x:c r="E6" t="n">
-        <x:v>25</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="F6" t="n">
-        <x:v>3</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="G6" t="inlineStr">
         <x:is>
@@ -1529,10 +1529,10 @@
         </x:is>
       </x:c>
       <x:c r="E7" t="n">
-        <x:v>16</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F7" t="n">
-        <x:v>2</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="G7" t="inlineStr">
         <x:is>
@@ -1557,10 +1557,10 @@
         </x:is>
       </x:c>
       <x:c r="E8" t="n">
-        <x:v>9</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="F8" t="n">
-        <x:v>2</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="G8" t="inlineStr">
         <x:is>
@@ -1585,10 +1585,10 @@
         </x:is>
       </x:c>
       <x:c r="E9" t="n">
-        <x:v>29</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="F9" t="n">
-        <x:v>2</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="G9" t="inlineStr">
         <x:is>
@@ -1613,10 +1613,10 @@
         </x:is>
       </x:c>
       <x:c r="E10" t="n">
-        <x:v>45</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="F10" t="n">
-        <x:v>2</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="G10" t="inlineStr">
         <x:is>
@@ -1641,10 +1641,10 @@
         </x:is>
       </x:c>
       <x:c r="E11" t="n">
-        <x:v>19</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F11" t="n">
-        <x:v>4</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="G11" t="inlineStr">
         <x:is>
@@ -1669,10 +1669,10 @@
         </x:is>
       </x:c>
       <x:c r="E12" t="n">
-        <x:v>17</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="F12" t="n">
-        <x:v>3</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="G12" t="inlineStr">
         <x:is>
@@ -1697,10 +1697,10 @@
         </x:is>
       </x:c>
       <x:c r="E13" t="n">
-        <x:v>41</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="F13" t="n">
-        <x:v>3</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="G13" t="inlineStr">
         <x:is>
@@ -1728,7 +1728,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F14" t="n">
-        <x:v>3</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="G14" t="inlineStr">
         <x:is>
@@ -1753,7 +1753,7 @@
         </x:is>
       </x:c>
       <x:c r="E15" t="n">
-        <x:v>9</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="F15" t="n">
         <x:v>0</x:v>
@@ -1781,10 +1781,10 @@
         </x:is>
       </x:c>
       <x:c r="E16" t="n">
-        <x:v>35</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="F16" t="n">
-        <x:v>4</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="G16" t="inlineStr">
         <x:is>
@@ -1809,10 +1809,10 @@
         </x:is>
       </x:c>
       <x:c r="E17" t="n">
-        <x:v>35</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="F17" t="n">
-        <x:v>3</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="G17" t="inlineStr">
         <x:is>

--- a/Excel/家具房间表.xlsx
+++ b/Excel/家具房间表.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="房间" sheetId="1" r:id="R189b7194a6704bed"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="网格" sheetId="2" r:id="R78b438265b7448e3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="占用格" sheetId="3" r:id="R859aedb57e0d4072"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="初始摆放" sheetId="4" r:id="R8884564ef8e2478e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="房间" sheetId="1" r:id="R685e072adfb44ade"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="网格" sheetId="2" r:id="R91604c8fc28d404b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="占用格" sheetId="3" r:id="Rbe582b84db2540e1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="初始摆放" sheetId="4" r:id="Rd82abcc1eda6441e"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -16,6 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:numFmts count="2">
+    <x:numFmt numFmtId="200" formatCode="0.###"/>
+    <x:numFmt numFmtId="201" formatCode="0"/>
+  </x:numFmts>
   <x:fonts count="5">
     <x:font>
       <x:sz val="11"/>
@@ -74,7 +78,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="5">
+  <x:cellXfs count="7">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0"/>
@@ -84,6 +88,8 @@
     <x:xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyAlignment="1">
       <x:alignment horizontal="center"/>
     </x:xf>
+    <x:xf numFmtId="200" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="201" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="常规" xfId="0"/>
@@ -952,307 +958,259 @@
       </x:c>
     </x:row>
     <x:row r="3">
-      <x:c r="A3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">living</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">wall</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">壁挂</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D3" t="n">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="E3" t="n">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="F3" t="n">
+      <x:c r="A3" t="str">
+        <x:v>living</x:v>
+      </x:c>
+      <x:c r="B3" t="str">
+        <x:v>wall</x:v>
+      </x:c>
+      <x:c r="C3" t="str">
+        <x:v>壁挂</x:v>
+      </x:c>
+      <x:c r="D3" s="5" t="n">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="E3" s="5" t="n">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="F3" s="5" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="G3" s="5" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="H3" s="5" t="n">
+        <x:v>373</x:v>
+      </x:c>
+      <x:c r="I3" s="5" t="n">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="J3" s="5" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" t="str">
+        <x:v>living</x:v>
+      </x:c>
+      <x:c r="B4" t="str">
+        <x:v>floor</x:v>
+      </x:c>
+      <x:c r="C4" t="str">
+        <x:v>地面</x:v>
+      </x:c>
+      <x:c r="D4" s="5" t="n">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="E4" s="5" t="n">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="G3" t="n">
+      <x:c r="F4" s="5" t="n">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="H3" t="n">
-        <x:v>316</x:v>
-      </x:c>
-      <x:c r="I3" t="n">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="J3" t="n">
+      <x:c r="G4" s="5" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="H4" s="5" t="n">
+        <x:v>78.5</x:v>
+      </x:c>
+      <x:c r="I4" s="5" t="n">
+        <x:v>452</x:v>
+      </x:c>
+      <x:c r="J4" s="5" t="n">
+        <x:v>0.603</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" t="str">
+        <x:v>bedroom</x:v>
+      </x:c>
+      <x:c r="B5" t="str">
+        <x:v>wall</x:v>
+      </x:c>
+      <x:c r="C5" t="str">
+        <x:v>壁挂</x:v>
+      </x:c>
+      <x:c r="D5" s="5" t="n">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="E5" s="5" t="n">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="F5" s="5" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="G5" s="5" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="H5" s="5" t="n">
+        <x:v>333.5</x:v>
+      </x:c>
+      <x:c r="I5" s="5" t="n">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="J5" s="5" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="4">
-      <x:c r="A4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">living</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">floor</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">地面</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D4" t="n">
-        <x:v>102</x:v>
-      </x:c>
-      <x:c r="E4" t="n">
+    <x:row r="6">
+      <x:c r="A6" t="str">
+        <x:v>bedroom</x:v>
+      </x:c>
+      <x:c r="B6" t="str">
+        <x:v>floor</x:v>
+      </x:c>
+      <x:c r="C6" t="str">
+        <x:v>地面</x:v>
+      </x:c>
+      <x:c r="D6" s="5" t="n">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="E6" s="5" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="F6" s="5" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="G6" s="5" t="n">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="F4" t="n">
+      <x:c r="H6" s="5" t="n">
+        <x:v>78.5</x:v>
+      </x:c>
+      <x:c r="I6" s="5" t="n">
+        <x:v>503</x:v>
+      </x:c>
+      <x:c r="J6" s="5" t="n">
+        <x:v>0.62</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" t="str">
+        <x:v>kitchen</x:v>
+      </x:c>
+      <x:c r="B7" t="str">
+        <x:v>wall</x:v>
+      </x:c>
+      <x:c r="C7" t="str">
+        <x:v>壁挂</x:v>
+      </x:c>
+      <x:c r="D7" s="5" t="n">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="E7" s="5" t="n">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="F7" s="5" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="G7" s="5" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="H7" s="5" t="n">
+        <x:v>645.5</x:v>
+      </x:c>
+      <x:c r="I7" s="5" t="n">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="J7" s="5" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" t="str">
+        <x:v>kitchen</x:v>
+      </x:c>
+      <x:c r="B8" t="str">
+        <x:v>floor</x:v>
+      </x:c>
+      <x:c r="C8" t="str">
+        <x:v>地面</x:v>
+      </x:c>
+      <x:c r="D8" s="5" t="n">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="E8" s="5" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="F8" s="5" t="n">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="G4" t="n">
-        <x:v>10.8</x:v>
-      </x:c>
-      <x:c r="H4" t="n">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="I4" t="n">
-        <x:v>500</x:v>
-      </x:c>
-      <x:c r="J4" t="n">
-        <x:v>0.65</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5">
-      <x:c r="A5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">bedroom</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">wall</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">壁挂</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D5" t="n">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="E5" t="n">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="F5" t="n">
+      <x:c r="G8" s="5" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="H8" s="5" t="n">
+        <x:v>78.5</x:v>
+      </x:c>
+      <x:c r="I8" s="5" t="n">
+        <x:v>498</x:v>
+      </x:c>
+      <x:c r="J8" s="5" t="n">
+        <x:v>0.56</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" t="str">
+        <x:v>study</x:v>
+      </x:c>
+      <x:c r="B9" t="str">
+        <x:v>wall</x:v>
+      </x:c>
+      <x:c r="C9" t="str">
+        <x:v>壁挂</x:v>
+      </x:c>
+      <x:c r="D9" s="5" t="n">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="E9" s="5" t="n">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="F9" s="5" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="G9" s="5" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="H9" s="5" t="n">
+        <x:v>310.5</x:v>
+      </x:c>
+      <x:c r="I9" s="5" t="n">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="J9" s="5" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" t="str">
+        <x:v>study</x:v>
+      </x:c>
+      <x:c r="B10" t="str">
+        <x:v>floor</x:v>
+      </x:c>
+      <x:c r="C10" t="str">
+        <x:v>地面</x:v>
+      </x:c>
+      <x:c r="D10" s="5" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="E10" s="5" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="F10" s="5" t="n">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="G5" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="H5" t="n">
-        <x:v>242</x:v>
-      </x:c>
-      <x:c r="I5" t="n">
-        <x:v>109</x:v>
-      </x:c>
-      <x:c r="J5" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6">
-      <x:c r="A6" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">bedroom</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B6" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">floor</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C6" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">地面</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D6" t="n">
-        <x:v>102</x:v>
-      </x:c>
-      <x:c r="E6" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F6" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="G6" t="n">
-        <x:v>10.5</x:v>
-      </x:c>
-      <x:c r="H6" t="n">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="I6" t="n">
-        <x:v>530</x:v>
-      </x:c>
-      <x:c r="J6" t="n">
-        <x:v>0.74</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7">
-      <x:c r="A7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">kitchen</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">wall</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">壁挂</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D7" t="n">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="E7" t="n">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="F7" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="G7" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="H7" t="n">
-        <x:v>562</x:v>
-      </x:c>
-      <x:c r="I7" t="n">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="J7" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8">
-      <x:c r="A8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">kitchen</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">floor</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">地面</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D8" t="n">
-        <x:v>102</x:v>
-      </x:c>
-      <x:c r="E8" t="n">
+      <x:c r="G10" s="5" t="n">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="F8" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="G8" t="n">
-        <x:v>10.4</x:v>
-      </x:c>
-      <x:c r="H8" t="n">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="I8" t="n">
-        <x:v>502</x:v>
-      </x:c>
-      <x:c r="J8" t="n">
-        <x:v>0.65</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9">
-      <x:c r="A9" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">study</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B9" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">wall</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C9" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">壁挂</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D9" t="n">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="E9" t="n">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="F9" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="G9" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="H9" t="n">
-        <x:v>130</x:v>
-      </x:c>
-      <x:c r="I9" t="n">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="J9" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10">
-      <x:c r="A10" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">study</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B10" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">floor</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C10" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">地面</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D10" t="n">
-        <x:v>102</x:v>
-      </x:c>
-      <x:c r="E10" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="F10" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="G10" t="n">
-        <x:v>10.05</x:v>
-      </x:c>
-      <x:c r="H10" t="n">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="I10" t="n">
-        <x:v>502</x:v>
-      </x:c>
-      <x:c r="J10" t="n">
-        <x:v>0.88</x:v>
+      <x:c r="H10" s="5" t="n">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="I10" s="5" t="n">
+        <x:v>469</x:v>
+      </x:c>
+      <x:c r="J10" s="5" t="n">
+        <x:v>0.69</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1401,424 +1359,346 @@
       </x:c>
     </x:row>
     <x:row r="3">
-      <x:c r="A3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">living</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">landscape_poster_02</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">wall</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E3" t="n">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="F3" t="n">
+      <x:c r="A3" t="str">
+        <x:v>living</x:v>
+      </x:c>
+      <x:c r="B3" t="str">
+        <x:v>landscape_poster_02</x:v>
+      </x:c>
+      <x:c r="C3" t="str">
+        <x:v>wall</x:v>
+      </x:c>
+      <x:c r="D3"/>
+      <x:c r="E3" s="6" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="F3" s="6" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="G3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">否</x:t>
-        </x:is>
+      <x:c r="G3" t="str">
+        <x:v>否</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">living</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">hanging_plant_01</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">wall</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E4" t="n">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="F4" t="n">
+      <x:c r="A4" t="str">
+        <x:v>living</x:v>
+      </x:c>
+      <x:c r="B4" t="str">
+        <x:v>hanging_plant_01</x:v>
+      </x:c>
+      <x:c r="C4" t="str">
+        <x:v>wall</x:v>
+      </x:c>
+      <x:c r="D4"/>
+      <x:c r="E4" s="6" t="n">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="F4" s="6" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="G4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">否</x:t>
-        </x:is>
+      <x:c r="G4" t="str">
+        <x:v>否</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">living</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">armchair_01</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">floor</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E5" t="n">
+      <x:c r="A5" t="str">
+        <x:v>living</x:v>
+      </x:c>
+      <x:c r="B5" t="str">
+        <x:v>armchair_01</x:v>
+      </x:c>
+      <x:c r="C5" t="str">
+        <x:v>floor</x:v>
+      </x:c>
+      <x:c r="D5"/>
+      <x:c r="E5" s="6" t="n">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="F5" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="G5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">否</x:t>
-        </x:is>
+      <x:c r="F5" s="6" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="G5" t="str">
+        <x:v>否</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">living</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B6" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">round_table_01</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C6" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">floor</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E6" t="n">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="F6" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="G6" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">否</x:t>
-        </x:is>
+      <x:c r="A6" t="str">
+        <x:v>living</x:v>
+      </x:c>
+      <x:c r="B6" t="str">
+        <x:v>round_table_01</x:v>
+      </x:c>
+      <x:c r="C6" t="str">
+        <x:v>floor</x:v>
+      </x:c>
+      <x:c r="D6"/>
+      <x:c r="E6" s="6" t="n">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="F6" s="6" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="G6" t="str">
+        <x:v>否</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
-      <x:c r="A7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">bedroom</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">landscape_poster_03</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">wall</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E7" t="n">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="F7" t="n">
+      <x:c r="A7" t="str">
+        <x:v>bedroom</x:v>
+      </x:c>
+      <x:c r="B7" t="str">
+        <x:v>landscape_poster_03</x:v>
+      </x:c>
+      <x:c r="C7" t="str">
+        <x:v>wall</x:v>
+      </x:c>
+      <x:c r="D7"/>
+      <x:c r="E7" s="6" t="n">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="F7" s="6" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G7" t="str">
+        <x:v>否</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" t="str">
+        <x:v>bedroom</x:v>
+      </x:c>
+      <x:c r="B8" t="str">
+        <x:v>single_sofa_02</x:v>
+      </x:c>
+      <x:c r="C8" t="str">
+        <x:v>floor</x:v>
+      </x:c>
+      <x:c r="D8"/>
+      <x:c r="E8" s="6" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="F8" s="6" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G8" t="str">
+        <x:v>否</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" t="str">
+        <x:v>bedroom</x:v>
+      </x:c>
+      <x:c r="B9" t="str">
+        <x:v>cat_sofa_01</x:v>
+      </x:c>
+      <x:c r="C9" t="str">
+        <x:v>floor</x:v>
+      </x:c>
+      <x:c r="D9"/>
+      <x:c r="E9" s="6" t="n">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="F9" s="6" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G9" t="str">
+        <x:v>否</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" t="str">
+        <x:v>bedroom</x:v>
+      </x:c>
+      <x:c r="B10" t="str">
+        <x:v>monstera_01</x:v>
+      </x:c>
+      <x:c r="C10" t="str">
+        <x:v>floor</x:v>
+      </x:c>
+      <x:c r="D10"/>
+      <x:c r="E10" s="6" t="n">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="F10" s="6" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G10" t="str">
+        <x:v>否</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" t="str">
+        <x:v>kitchen</x:v>
+      </x:c>
+      <x:c r="B11" t="str">
+        <x:v>vintage_square_clock_02</x:v>
+      </x:c>
+      <x:c r="C11" t="str">
+        <x:v>wall</x:v>
+      </x:c>
+      <x:c r="D11"/>
+      <x:c r="E11" s="6" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="F11" s="6" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="G11" t="str">
+        <x:v>否</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" t="str">
+        <x:v>kitchen</x:v>
+      </x:c>
+      <x:c r="B12" t="str">
+        <x:v>round_table_02</x:v>
+      </x:c>
+      <x:c r="C12" t="str">
+        <x:v>floor</x:v>
+      </x:c>
+      <x:c r="D12"/>
+      <x:c r="E12" s="6" t="n">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="F12" s="6" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G12" t="str">
+        <x:v>否</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" t="str">
+        <x:v>kitchen</x:v>
+      </x:c>
+      <x:c r="B13" t="str">
+        <x:v>potted_plant_01</x:v>
+      </x:c>
+      <x:c r="C13" t="str">
+        <x:v>floor</x:v>
+      </x:c>
+      <x:c r="D13"/>
+      <x:c r="E13" s="6" t="n">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="F13" s="6" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="G7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">否</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="8">
-      <x:c r="A8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">bedroom</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">single_sofa_02</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">floor</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E8" t="n">
+      <x:c r="G13" t="str">
+        <x:v>否</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" t="str">
+        <x:v>study</x:v>
+      </x:c>
+      <x:c r="B14" t="str">
+        <x:v>round_table_03</x:v>
+      </x:c>
+      <x:c r="C14" t="str">
+        <x:v>floor</x:v>
+      </x:c>
+      <x:c r="D14"/>
+      <x:c r="E14" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F14" s="6" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G14" t="str">
+        <x:v>否</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" t="str">
+        <x:v>study</x:v>
+      </x:c>
+      <x:c r="B15" t="str">
+        <x:v>potted_plant_02</x:v>
+      </x:c>
+      <x:c r="C15" t="str">
+        <x:v>floor</x:v>
+      </x:c>
+      <x:c r="D15"/>
+      <x:c r="E15" s="6" t="n">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="F8" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="G8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">否</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="9">
-      <x:c r="A9" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">bedroom</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B9" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">cat_sofa_01</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C9" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">floor</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E9" t="n">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="F9" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="G9" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">否</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="10">
-      <x:c r="A10" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">bedroom</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B10" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">monstera_01</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C10" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">floor</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E10" t="n">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="F10" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="G10" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">否</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="11">
-      <x:c r="A11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">kitchen</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">vintage_square_clock_02</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">wall</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E11" t="n">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="F11" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="G11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">否</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="12">
-      <x:c r="A12" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">kitchen</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B12" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">round_table_02</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C12" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">floor</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E12" t="n">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="F12" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="G12" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">否</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="13">
-      <x:c r="A13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">kitchen</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">potted_plant_01</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">floor</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E13" t="n">
-        <x:v>82</x:v>
-      </x:c>
-      <x:c r="F13" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="G13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">否</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="14">
-      <x:c r="A14" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">study</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B14" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">round_table_03</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C14" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">floor</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E14" t="n">
+      <x:c r="F15" s="6" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F14" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="G14" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">否</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="15">
-      <x:c r="A15" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">study</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B15" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">potted_plant_02</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C15" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">floor</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E15" t="n">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="F15" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G15" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">否</x:t>
-        </x:is>
+      <x:c r="G15" t="str">
+        <x:v>否</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
-      <x:c r="A16" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">study</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B16" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">vintage_square_clock_03</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C16" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">wall</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E16" t="n">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="F16" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="G16" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">否</x:t>
-        </x:is>
+      <x:c r="A16" t="str">
+        <x:v>study</x:v>
+      </x:c>
+      <x:c r="B16" t="str">
+        <x:v>vintage_square_clock_03</x:v>
+      </x:c>
+      <x:c r="C16" t="str">
+        <x:v>wall</x:v>
+      </x:c>
+      <x:c r="D16"/>
+      <x:c r="E16" s="6" t="n">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="F16" s="6" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="G16" t="str">
+        <x:v>否</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
-      <x:c r="A17" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">study</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B17" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">single_sofa_04</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C17" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">floor</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E17" t="n">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="F17" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="G17" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">否</x:t>
-        </x:is>
-      </x:c>
+      <x:c r="A17" t="str">
+        <x:v>study</x:v>
+      </x:c>
+      <x:c r="B17" t="str">
+        <x:v>single_sofa_04</x:v>
+      </x:c>
+      <x:c r="C17" t="str">
+        <x:v>floor</x:v>
+      </x:c>
+      <x:c r="D17"/>
+      <x:c r="E17" s="6" t="n">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="F17" s="6" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G17" t="str">
+        <x:v>否</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18"/>
+      <x:c r="B18"/>
+      <x:c r="C18"/>
+      <x:c r="D18"/>
+      <x:c r="E18" s="6"/>
+      <x:c r="F18" s="6"/>
+      <x:c r="G18"/>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19"/>
+      <x:c r="B19"/>
+      <x:c r="C19"/>
+      <x:c r="D19"/>
+      <x:c r="E19" s="6"/>
+      <x:c r="F19" s="6"/>
+      <x:c r="G19"/>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20"/>
+      <x:c r="B20"/>
+      <x:c r="C20"/>
+      <x:c r="D20"/>
+      <x:c r="E20" s="6"/>
+      <x:c r="F20" s="6"/>
+      <x:c r="G20"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Excel/家具房间表.xlsx
+++ b/Excel/家具房间表.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="房间" sheetId="1" r:id="R685e072adfb44ade"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="网格" sheetId="2" r:id="R91604c8fc28d404b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="占用格" sheetId="3" r:id="Rbe582b84db2540e1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="初始摆放" sheetId="4" r:id="Rd82abcc1eda6441e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="房间" sheetId="1" r:id="R41d1feeeb45a4a70"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="网格" sheetId="2" r:id="R42ea7346d5c541ee"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="占用格" sheetId="3" r:id="R7f472517549f4be2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="初始摆放" sheetId="4" r:id="R9ac6f38ed209449f"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -644,13 +644,13 @@
         <x:v>0.7943</x:v>
       </x:c>
       <x:c r="R3" t="n">
-        <x:v>0.8015</x:v>
+        <x:v>0.7943</x:v>
       </x:c>
       <x:c r="S3" t="n">
-        <x:v>0.99</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="T3" t="n">
-        <x:v>13.2</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -706,13 +706,13 @@
         <x:v>0.832</x:v>
       </x:c>
       <x:c r="R4" t="n">
-        <x:v>0.8931</x:v>
+        <x:v>0.832</x:v>
       </x:c>
       <x:c r="S4" t="n">
-        <x:v>1.062</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="T4" t="n">
-        <x:v>47.9</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -768,13 +768,13 @@
         <x:v>0.7853</x:v>
       </x:c>
       <x:c r="R5" t="n">
-        <x:v>0.7825</x:v>
+        <x:v>0.7853</x:v>
       </x:c>
       <x:c r="S5" t="n">
-        <x:v>1.066</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="T5" t="n">
-        <x:v>171.1</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -830,7 +830,7 @@
         <x:v>0.8</x:v>
       </x:c>
       <x:c r="R6" t="n">
-        <x:v>0.8753</x:v>
+        <x:v>0.8</x:v>
       </x:c>
       <x:c r="S6" t="n">
         <x:v>1</x:v>

--- a/Excel/家具房间表.xlsx
+++ b/Excel/家具房间表.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="房间" sheetId="1" r:id="R41d1feeeb45a4a70"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="网格" sheetId="2" r:id="R42ea7346d5c541ee"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="占用格" sheetId="3" r:id="R7f472517549f4be2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="初始摆放" sheetId="4" r:id="R9ac6f38ed209449f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="房间" sheetId="1" r:id="R7f428160136f4369"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="网格" sheetId="2" r:id="Rcaf54a69451e46b9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="占用格" sheetId="3" r:id="Rd21f863c302f47e2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="初始摆放" sheetId="4" r:id="Rcc9c829e009e4afe"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1412,10 +1412,10 @@
       </x:c>
       <x:c r="D5"/>
       <x:c r="E5" s="6" t="n">
-        <x:v>34</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="F5" s="6" t="n">
-        <x:v>7</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="G5" t="str">
         <x:v>否</x:v>
@@ -1433,10 +1433,10 @@
       </x:c>
       <x:c r="D6"/>
       <x:c r="E6" s="6" t="n">
-        <x:v>49</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="F6" s="6" t="n">
-        <x:v>7</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G6" t="str">
         <x:v>否</x:v>
@@ -1475,10 +1475,10 @@
       </x:c>
       <x:c r="D8"/>
       <x:c r="E8" s="6" t="n">
-        <x:v>18</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="F8" s="6" t="n">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="G8" t="str">
         <x:v>否</x:v>
@@ -1496,10 +1496,10 @@
       </x:c>
       <x:c r="D9"/>
       <x:c r="E9" s="6" t="n">
-        <x:v>57</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="F9" s="6" t="n">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="G9" t="str">
         <x:v>否</x:v>
@@ -1517,10 +1517,10 @@
       </x:c>
       <x:c r="D10"/>
       <x:c r="E10" s="6" t="n">
-        <x:v>89</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="F10" s="6" t="n">
-        <x:v>3</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="G10" t="str">
         <x:v>否</x:v>
@@ -1559,10 +1559,10 @@
       </x:c>
       <x:c r="D12"/>
       <x:c r="E12" s="6" t="n">
-        <x:v>34</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="F12" s="6" t="n">
-        <x:v>3</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="G12" t="str">
         <x:v>否</x:v>
@@ -1580,10 +1580,10 @@
       </x:c>
       <x:c r="D13"/>
       <x:c r="E13" s="6" t="n">
-        <x:v>81</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="F13" s="6" t="n">
-        <x:v>4</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="G13" t="str">
         <x:v>否</x:v>
@@ -1601,10 +1601,10 @@
       </x:c>
       <x:c r="D14"/>
       <x:c r="E14" s="6" t="n">
-        <x:v>0</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="F14" s="6" t="n">
-        <x:v>5</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="G14" t="str">
         <x:v>否</x:v>
@@ -1622,10 +1622,10 @@
       </x:c>
       <x:c r="D15"/>
       <x:c r="E15" s="6" t="n">
-        <x:v>18</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="F15" s="6" t="n">
-        <x:v>0</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="G15" t="str">
         <x:v>否</x:v>
@@ -1664,10 +1664,10 @@
       </x:c>
       <x:c r="D17"/>
       <x:c r="E17" s="6" t="n">
-        <x:v>69</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="F17" s="6" t="n">
-        <x:v>5</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="G17" t="str">
         <x:v>否</x:v>

--- a/Excel/家具房间表.xlsx
+++ b/Excel/家具房间表.xlsx
@@ -1343,7 +1343,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="3"/>
@@ -1433,19 +1433,19 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>landscape_poster_02</t>
+          <t>bed_front_01</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>wall</t>
-        </is>
-      </c>
-      <c r="E3" s="8" t="n">
-        <v>18</v>
-      </c>
-      <c r="F3" s="8" t="n">
-        <v>6</v>
+          <t>floor</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>45</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -1461,7 +1461,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>hanging_plant_01</t>
+          <t>landscape_poster_02</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1470,7 +1470,7 @@
         </is>
       </c>
       <c r="E4" s="8" t="n">
-        <v>56</v>
+        <v>18</v>
       </c>
       <c r="F4" s="8" t="n">
         <v>6</v>
@@ -1489,19 +1489,19 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>armchair_01</t>
+          <t>hanging_plant_01</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>floor</t>
+          <t>wall</t>
         </is>
       </c>
       <c r="E5" s="8" t="n">
-        <v>35</v>
+        <v>56</v>
       </c>
       <c r="F5" s="8" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1517,7 +1517,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>round_table_01</t>
+          <t>armchair_01</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1526,10 +1526,10 @@
         </is>
       </c>
       <c r="E6" s="8" t="n">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1540,24 +1540,24 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>bedroom</t>
+          <t>living</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>landscape_poster_03</t>
+          <t>round_table_01</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>wall</t>
+          <t>floor</t>
         </is>
       </c>
       <c r="E7" s="8" t="n">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="F7" s="8" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1573,7 +1573,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>single_sofa_02</t>
+          <t>bed_front_02</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1581,11 +1581,11 @@
           <t>floor</t>
         </is>
       </c>
-      <c r="E8" s="8" t="n">
-        <v>19</v>
-      </c>
-      <c r="F8" s="8" t="n">
-        <v>5</v>
+      <c r="E8" t="n">
+        <v>45</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -1601,16 +1601,16 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>cat_sofa_01</t>
+          <t>landscape_poster_03</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>floor</t>
+          <t>wall</t>
         </is>
       </c>
       <c r="E9" s="8" t="n">
-        <v>58</v>
+        <v>35</v>
       </c>
       <c r="F9" s="8" t="n">
         <v>5</v>
@@ -1629,7 +1629,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>monstera_01</t>
+          <t>single_sofa_02</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1638,10 +1638,10 @@
         </is>
       </c>
       <c r="E10" s="8" t="n">
-        <v>92</v>
+        <v>19</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -1652,24 +1652,24 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>kitchen</t>
+          <t>bedroom</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>vintage_square_clock_02</t>
+          <t>cat_sofa_01</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>wall</t>
+          <t>floor</t>
         </is>
       </c>
       <c r="E11" s="8" t="n">
-        <v>40</v>
+        <v>58</v>
       </c>
       <c r="F11" s="8" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -1680,12 +1680,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>kitchen</t>
+          <t>bedroom</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>round_table_02</t>
+          <t>monstera_01</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1694,10 +1694,10 @@
         </is>
       </c>
       <c r="E12" s="8" t="n">
-        <v>36</v>
+        <v>92</v>
       </c>
       <c r="F12" s="8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -1713,7 +1713,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>potted_plant_01</t>
+          <t>bed_front_03</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1721,11 +1721,11 @@
           <t>floor</t>
         </is>
       </c>
-      <c r="E13" s="8" t="n">
-        <v>82</v>
-      </c>
-      <c r="F13" s="8" t="n">
-        <v>7</v>
+      <c r="E13" t="n">
+        <v>45</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -1736,24 +1736,24 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>study</t>
+          <t>kitchen</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>round_table_03</t>
+          <t>vintage_square_clock_02</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>floor</t>
+          <t>wall</t>
         </is>
       </c>
       <c r="E14" s="8" t="n">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="F14" s="8" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1764,12 +1764,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>study</t>
+          <t>kitchen</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>potted_plant_02</t>
+          <t>round_table_02</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1778,10 +1778,10 @@
         </is>
       </c>
       <c r="E15" s="8" t="n">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="F15" s="8" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1792,24 +1792,24 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>study</t>
+          <t>kitchen</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>vintage_square_clock_03</t>
+          <t>potted_plant_01</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>wall</t>
+          <t>floor</t>
         </is>
       </c>
       <c r="E16" s="8" t="n">
-        <v>66</v>
+        <v>82</v>
       </c>
       <c r="F16" s="8" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1825,37 +1825,149 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
+          <t>bed_front_04</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>floor</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>44</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>study</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>round_table_03</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>floor</t>
+        </is>
+      </c>
+      <c r="E18" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="F18" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>study</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>potted_plant_02</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>floor</t>
+        </is>
+      </c>
+      <c r="E19" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="F19" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>study</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>vintage_square_clock_03</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>wall</t>
+        </is>
+      </c>
+      <c r="E20" s="8" t="n">
+        <v>66</v>
+      </c>
+      <c r="F20" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>study</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
           <t>single_sofa_04</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>floor</t>
         </is>
       </c>
-      <c r="E17" s="8" t="n">
+      <c r="E21" s="8" t="n">
         <v>70</v>
       </c>
-      <c r="F17" s="8" t="n">
+      <c r="F21" s="8" t="n">
         <v>7</v>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="E18" s="8" t="n"/>
-      <c r="F18" s="8" t="n"/>
-    </row>
-    <row r="19">
-      <c r="E19" s="8" t="n"/>
-      <c r="F19" s="8" t="n"/>
-    </row>
-    <row r="20">
-      <c r="E20" s="8" t="n"/>
-      <c r="F20" s="8" t="n"/>
+    <row r="22">
+      <c r="E22" s="8" t="n"/>
+      <c r="F22" s="8" t="n"/>
+    </row>
+    <row r="23">
+      <c r="E23" s="8" t="n"/>
+      <c r="F23" s="8" t="n"/>
+    </row>
+    <row r="24">
+      <c r="E24" s="8" t="n"/>
+      <c r="F24" s="8" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
